--- a/TEngine/Configs/GameConfig/Datas/Reward.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Reward.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xx\NewText\TEngine\Configs\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19C43A94-2C3B-4178-B9A0-69280A96C3B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAB1038-3BF7-4FC4-A1F6-9269F9A2DD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32595" yWindow="2850" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="reward" sheetId="1" r:id="rId1"/>
@@ -677,7 +677,7 @@
         <v>11</v>
       </c>
       <c r="D6" s="6">
-        <v>10002</v>
+        <v>10003</v>
       </c>
       <c r="E6" s="6">
         <v>1</v>

--- a/TEngine/Configs/GameConfig/Datas/Reward.xlsx
+++ b/TEngine/Configs/GameConfig/Datas/Reward.xlsx
@@ -652,7 +652,7 @@
         <v>10000</v>
       </c>
       <c r="E4" s="6">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.2">
